--- a/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/EstItens_2EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_2EM_MT/Simulado_III/EstItens_2EM_MT_S3.xlsx
@@ -473,19 +473,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1.02242714779073</v>
+        <v>1.02775610242716</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41923222750166</v>
+        <v>1.43313171824228</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0204485429558145</v>
+        <v>0.0205551220485432</v>
       </c>
       <c r="E2" t="n">
-        <v>320.961611375083</v>
+        <v>321.656585912114</v>
       </c>
       <c r="F2" t="n">
-        <v>0.017133038209742</v>
+        <v>0.0171517701030771</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -496,19 +496,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.182778430139589</v>
+        <v>0.182820921356007</v>
       </c>
       <c r="C3" t="n">
-        <v>4.79930977775088</v>
+        <v>4.82002867339313</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00365556860279178</v>
+        <v>0.00365641842712013</v>
       </c>
       <c r="E3" t="n">
-        <v>489.965488887544</v>
+        <v>491.001433669656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0459882824458235</v>
+        <v>0.0463669164004182</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -519,19 +519,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>2.26596614775884</v>
+        <v>2.2722049052222</v>
       </c>
       <c r="C4" t="n">
-        <v>2.19308960864848</v>
+        <v>2.19818953808857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0453193229551767</v>
+        <v>0.0454440981044441</v>
       </c>
       <c r="E4" t="n">
-        <v>359.654480432424</v>
+        <v>359.909476904428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.239138866944971</v>
+        <v>0.238340965770686</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -545,10 +545,10 @@
         <v>1.55</v>
       </c>
       <c r="C5" t="n">
-        <v>2.67338000000001</v>
+        <v>2.67338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0309999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="E5" t="n">
         <v>383.669</v>
@@ -565,22 +565,22 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>0.349999999999999</v>
+        <v>1.42894783247731</v>
       </c>
       <c r="C6" t="n">
-        <v>5.44448000000001</v>
+        <v>4.78956012071593</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00699999999999998</v>
+        <v>0.0285789566495462</v>
       </c>
       <c r="E6" t="n">
-        <v>522.224</v>
+        <v>489.478006035797</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0710000000000003</v>
+        <v>0.180261699779183</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0627797687673</v>
+        <v>1.06277976876731</v>
       </c>
       <c r="C8" t="n">
         <v>3.25034579224714</v>
@@ -637,16 +637,16 @@
         <v>1.44617244574152</v>
       </c>
       <c r="C9" t="n">
-        <v>2.66265077769933</v>
+        <v>2.66265077769934</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0289234489148304</v>
+        <v>0.0289234489148303</v>
       </c>
       <c r="E9" t="n">
         <v>383.132538884967</v>
       </c>
       <c r="F9" t="n">
-        <v>0.175890036350279</v>
+        <v>0.17589003635028</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -657,19 +657,19 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.49667008777781</v>
+        <v>2.48900421147964</v>
       </c>
       <c r="C10" t="n">
-        <v>2.43764812260016</v>
+        <v>2.44108768946054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0499334017555563</v>
+        <v>0.0497800842295928</v>
       </c>
       <c r="E10" t="n">
-        <v>371.882406130008</v>
+        <v>372.054384473027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.191343196157891</v>
+        <v>0.190270243731821</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
@@ -680,19 +680,19 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.42280551209641</v>
+        <v>1.42323924536663</v>
       </c>
       <c r="C11" t="n">
-        <v>2.47103274416528</v>
+        <v>2.47468362749802</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0284561102419283</v>
+        <v>0.0284647849073325</v>
       </c>
       <c r="E11" t="n">
-        <v>373.551637208264</v>
+        <v>373.734181374901</v>
       </c>
       <c r="F11" t="n">
-        <v>0.180650179985081</v>
+        <v>0.17946956550832</v>
       </c>
       <c r="G11" t="s">
         <v>8</v>
@@ -703,7 +703,7 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.70485770995117</v>
+        <v>1.70485770995118</v>
       </c>
       <c r="C12" t="n">
         <v>2.21387696226408</v>
@@ -749,7 +749,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>1.22742731801847</v>
+        <v>1.22742731801846</v>
       </c>
       <c r="C14" t="n">
         <v>2.67255617837512</v>
@@ -761,7 +761,7 @@
         <v>383.627808918756</v>
       </c>
       <c r="F14" t="n">
-        <v>0.193535074744009</v>
+        <v>0.193535074744008</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -801,7 +801,7 @@
         <v>2.35786</v>
       </c>
       <c r="D16" t="n">
-        <v>0.057</v>
+        <v>0.0570000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>367.893</v>
@@ -818,19 +818,19 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>2.66611995977289</v>
+        <v>2.66464947475183</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3643446228753</v>
+        <v>2.36795098985521</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0533223991954578</v>
+        <v>0.0532929894950365</v>
       </c>
       <c r="E17" t="n">
-        <v>368.217231143765</v>
+        <v>368.397549492761</v>
       </c>
       <c r="F17" t="n">
-        <v>0.163476261050643</v>
+        <v>0.162466779260297</v>
       </c>
       <c r="G17" t="s">
         <v>8</v>
@@ -841,19 +841,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.47499368822474</v>
+        <v>1.47486113695359</v>
       </c>
       <c r="C18" t="n">
-        <v>3.55515520998215</v>
+        <v>3.55808851397522</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0294998737644947</v>
+        <v>0.0294972227390718</v>
       </c>
       <c r="E18" t="n">
-        <v>427.757760499108</v>
+        <v>427.904425698761</v>
       </c>
       <c r="F18" t="n">
-        <v>0.197588910237286</v>
+        <v>0.197231728683819</v>
       </c>
       <c r="G18" t="s">
         <v>8</v>
@@ -867,10 +867,10 @@
         <v>1.54104954143406</v>
       </c>
       <c r="C19" t="n">
-        <v>2.93556623650523</v>
+        <v>2.93556623650522</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0308209908286811</v>
+        <v>0.0308209908286812</v>
       </c>
       <c r="E19" t="n">
         <v>396.778311825261</v>
@@ -890,7 +890,7 @@
         <v>2.61541934777186</v>
       </c>
       <c r="C20" t="n">
-        <v>2.57156058184517</v>
+        <v>2.57156058184516</v>
       </c>
       <c r="D20" t="n">
         <v>0.0523083869554372</v>
@@ -910,19 +910,19 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>0.315058689447332</v>
+        <v>0.316896217780202</v>
       </c>
       <c r="C21" t="n">
-        <v>4.4330977883949</v>
+        <v>4.4165952116713</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00630117378894664</v>
+        <v>0.00633792435560404</v>
       </c>
       <c r="E21" t="n">
-        <v>471.654889419745</v>
+        <v>470.829760583565</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0633161106344132</v>
+        <v>0.0622998973468343</v>
       </c>
       <c r="G21" t="s">
         <v>8</v>
@@ -933,19 +933,19 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.22539680568554</v>
+        <v>1.24484282890571</v>
       </c>
       <c r="C22" t="n">
-        <v>3.8048727214135</v>
+        <v>3.79488748786659</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0245079361137108</v>
+        <v>0.0248968565781142</v>
       </c>
       <c r="E22" t="n">
-        <v>440.243636070675</v>
+        <v>439.74437439333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.167865500389049</v>
+        <v>0.168270527318605</v>
       </c>
       <c r="G22" t="s">
         <v>8</v>
@@ -956,19 +956,19 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>1.25059970266018</v>
+        <v>1.25622846601497</v>
       </c>
       <c r="C23" t="n">
-        <v>3.27043048951259</v>
+        <v>3.27007055651043</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0250119940532037</v>
+        <v>0.0251245693202994</v>
       </c>
       <c r="E23" t="n">
-        <v>413.521524475629</v>
+        <v>413.503527825522</v>
       </c>
       <c r="F23" t="n">
-        <v>0.210710742915288</v>
+        <v>0.210286859455238</v>
       </c>
       <c r="G23" t="s">
         <v>8</v>
@@ -979,19 +979,19 @@
         <v>31</v>
       </c>
       <c r="B24" t="n">
-        <v>0.702106332645512</v>
+        <v>0.698191811054233</v>
       </c>
       <c r="C24" t="n">
-        <v>2.15632591352928</v>
+        <v>2.14386103019511</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0140421266529102</v>
+        <v>0.0139638362210847</v>
       </c>
       <c r="E24" t="n">
-        <v>357.816295676464</v>
+        <v>357.193051509755</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0869173051528478</v>
+        <v>0.0809040625609673</v>
       </c>
       <c r="G24" t="s">
         <v>8</v>
@@ -1002,19 +1002,19 @@
         <v>32</v>
       </c>
       <c r="B25" t="n">
-        <v>4.34983449397825</v>
+        <v>4.3431282427612</v>
       </c>
       <c r="C25" t="n">
-        <v>2.70214032727331</v>
+        <v>2.70706508067923</v>
       </c>
       <c r="D25" t="n">
-        <v>0.086996689879565</v>
+        <v>0.0868625648552239</v>
       </c>
       <c r="E25" t="n">
-        <v>385.107016363666</v>
+        <v>385.353254033961</v>
       </c>
       <c r="F25" t="n">
-        <v>0.223598630905842</v>
+        <v>0.223464653810371</v>
       </c>
       <c r="G25" t="s">
         <v>8</v>
@@ -1025,19 +1025,19 @@
         <v>33</v>
       </c>
       <c r="B26" t="n">
-        <v>2.52885012863823</v>
+        <v>2.51902746793252</v>
       </c>
       <c r="C26" t="n">
-        <v>2.67149606532309</v>
+        <v>2.67506228692081</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0505770025727646</v>
+        <v>0.0503805493586505</v>
       </c>
       <c r="E26" t="n">
-        <v>383.574803266155</v>
+        <v>383.75311434604</v>
       </c>
       <c r="F26" t="n">
-        <v>0.192353471697883</v>
+        <v>0.191563320484069</v>
       </c>
       <c r="G26" t="s">
         <v>8</v>
@@ -1051,7 +1051,7 @@
         <v>2.3242653531958</v>
       </c>
       <c r="C27" t="n">
-        <v>2.81373560338527</v>
+        <v>2.81373560338525</v>
       </c>
       <c r="D27" t="n">
         <v>0.046485307063916</v>
